--- a/quizzes/010_solow_growth_model_quiz--quizzes.xlsx
+++ b/quizzes/010_solow_growth_model_quiz--quizzes.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="37" customWidth="1" min="2" max="2"/>
+    <col width="37" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_10,_'name':_'solow_growth_model_quiz_3_10',_'label':_'solow_growth_model_quiz_3_10_label'}</t>
+          <t>solow_growth_model_quiz_3_10_label</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 10, 'name': 'solow_growth_model_quiz_3_10', 'label': 'solow_growth_model_quiz_3_10_label'}</t>
+          <t>solow growth model quiz 3 10 label</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_20,_'name':_'solow_growth_model_quiz_3_20',_'label':_'solow_growth_model_quiz_3_20_label'}</t>
+          <t>solow_growth_model_quiz_3_20_label</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 20, 'name': 'solow_growth_model_quiz_3_20', 'label': 'solow_growth_model_quiz_3_20_label'}</t>
+          <t>solow growth model quiz 3 20 label</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_30,_'name':_'solow_growth_model_quiz_18_30',_'label':_'solow_growth_model_quiz_18_30_label'}</t>
+          <t>solow_growth_model_quiz_18_30_label</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 30, 'name': 'solow_growth_model_quiz_18_30', 'label': 'solow_growth_model_quiz_18_30_label'}</t>
+          <t>solow growth model quiz 18 30 label</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_31,_'name':_'solow_growth_model_quiz_18_31',_'label':_'solow_growth_model_quiz_18_31_label'}</t>
+          <t>solow_growth_model_quiz_18_31_label</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 31, 'name': 'solow_growth_model_quiz_18_31', 'label': 'solow_growth_model_quiz_18_31_label'}</t>
+          <t>solow growth model quiz 18 31 label</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_32,_'name':_'solow_growth_model_quiz_19_32',_'label':_'solow_growth_model_quiz_19_32_label'}</t>
+          <t>solow_growth_model_quiz_19_32_label</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 32, 'name': 'solow_growth_model_quiz_19_32', 'label': 'solow_growth_model_quiz_19_32_label'}</t>
+          <t>solow growth model quiz 19 32 label</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_33,_'name':_'solow_growth_model_quiz_19_33',_'label':_'solow_growth_model_quiz_19_33_label'}</t>
+          <t>solow_growth_model_quiz_19_33_label</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 33, 'name': 'solow_growth_model_quiz_19_33', 'label': 'solow_growth_model_quiz_19_33_label'}</t>
+          <t>solow growth model quiz 19 33 label</t>
         </is>
       </c>
     </row>
